--- a/case_studies/high_feedstock_availability_5_dd/2050/technologies.xlsx
+++ b/case_studies/high_feedstock_availability_5_dd/2050/technologies.xlsx
@@ -691,16 +691,16 @@
         <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>115.62</v>
+        <v>115.26</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>481.02</v>
+        <v>455.5</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>128.65</v>
+        <v>0</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>57.64</v>
+        <v>24.07</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>946.41</v>
@@ -712,37 +712,37 @@
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>378.95</v>
+        <v>281.68</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>501.68</v>
+        <v>334.05</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>32.7</v>
+        <v>35.44</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>42.53</v>
+        <v>23.37</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>173.26</v>
+        <v>159.94</v>
       </c>
       <c r="U2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>186.96</v>
+        <v>69.83</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>267.23</v>
+        <v>241.86</v>
       </c>
       <c r="X2" s="3" t="n">
-        <v>11.99</v>
+        <v>6.85</v>
       </c>
       <c r="Y2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>34.14</v>
+        <v>0</v>
       </c>
       <c r="AA2" s="3" t="n">
         <v>0</v>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>0</v>
@@ -779,16 +779,16 @@
         <v>0</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>8.08</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>3.55</v>
+        <v>0.32</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>0</v>
+        <v>17.75</v>
       </c>
       <c r="J3" s="5" t="n">
         <v>35.39</v>
@@ -836,10 +836,10 @@
         <v>0</v>
       </c>
       <c r="Y3" s="5" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="Z3" s="5" t="n">
-        <v>44.46</v>
+        <v>44.45</v>
       </c>
       <c r="AA3" s="5" t="n">
         <v>0</v>
@@ -885,52 +885,52 @@
         <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>441.41</v>
+        <v>56.57</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>842.47</v>
+        <v>518.86</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>223.62</v>
+        <v>295.87</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>438.77</v>
+        <v>1435.04</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>438.77</v>
+        <v>1369.36</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>1562.46</v>
+        <v>741.87</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>1675.41</v>
+        <v>784.39</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>264.6</v>
+        <v>0</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>86.64</v>
+        <v>47.61</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>665.03</v>
+        <v>352.44</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>54.5</v>
+        <v>13.99</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>249.78</v>
+        <v>332.2</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>23.97</v>
+        <v>13.7</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>0</v>
@@ -964,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26.37</v>
+        <v>0</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>216.89</v>
@@ -982,16 +982,16 @@
         <v>0</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>108.65</v>
+        <v>108.43</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>513.04</v>
+        <v>318.16</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>175.85</v>
+        <v>148.52</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>0.14</v>
+        <v>156.59</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>745.4</v>
@@ -1003,34 +1003,34 @@
         <v>0</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>87.81999999999999</v>
+        <v>549.62</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>130.65</v>
+        <v>561.59</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>28.54</v>
+        <v>8</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>125.97</v>
+        <v>265.02</v>
       </c>
       <c r="U5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="V5" s="5" t="n">
-        <v>2.74</v>
+        <v>0.64</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>249.98</v>
+        <v>548.34</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>23.97</v>
+        <v>13.7</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>2630.07</v>
+        <v>40789.13</v>
       </c>
       <c r="Z5" s="5" t="n">
         <v>204.22</v>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>89.48999999999999</v>
+        <v>91.61</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>385.33</v>
+        <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>62.79</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>11.11</v>
@@ -1079,52 +1079,52 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>67.03</v>
+        <v>67.83</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>163.14</v>
+        <v>174.67</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>42.99</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>162.27</v>
+        <v>165.37</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>174.71</v>
+        <v>197.83</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>174.71</v>
+        <v>565.33</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>531.3</v>
+        <v>487.08</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>551.1900000000001</v>
+        <v>508.29</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>67.84</v>
+        <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>13.53</v>
+        <v>14.27</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>229.3</v>
+        <v>233.2</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>67.84</v>
+        <v>75.75</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>23.97</v>
+        <v>13.7</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>0</v>
@@ -1158,7 +1158,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>99.95999999999999</v>
+        <v>0</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>23.07</v>
+        <v>0</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>59.3</v>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>0</v>
+        <v>35.68</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>0</v>
@@ -1203,10 +1203,10 @@
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>25.76</v>
+        <v>19.87</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>25.97</v>
+        <v>15.89</v>
       </c>
       <c r="T7" s="5" t="n">
         <v>48.52</v>
@@ -1215,16 +1215,16 @@
         <v>0</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>25.6</v>
+        <v>48.1</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>0</v>
+        <v>2934.72</v>
       </c>
       <c r="Z7" s="5" t="n">
         <v>0</v>
@@ -1273,16 +1273,16 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>66.12</v>
+        <v>136.69</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>278.28</v>
+        <v>288.62</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>47.4</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>148.29</v>
+        <v>80.28</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>136.33</v>
@@ -1294,34 +1294,34 @@
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>447.37</v>
+        <v>461.32</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>519.23</v>
+        <v>491.16</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>174.64</v>
+        <v>102.32</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>106.83</v>
+        <v>50.29</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>214.41</v>
+        <v>216.97</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>8.67</v>
+        <v>2.05</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>172.28</v>
+        <v>432.76</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>23.97</v>
+        <v>13.7</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>6265.9</v>
+        <v>36308.58</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>0</v>

--- a/case_studies/high_feedstock_availability_5_dd/2050/technologies.xlsx
+++ b/case_studies/high_feedstock_availability_5_dd/2050/technologies.xlsx
@@ -691,16 +691,16 @@
         <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>115.26</v>
+        <v>113.79</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>455.5</v>
+        <v>534.54</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0</v>
+        <v>65.64</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>24.07</v>
+        <v>0</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>946.41</v>
@@ -712,16 +712,16 @@
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>281.68</v>
+        <v>227.58</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>334.05</v>
+        <v>386.47</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>35.44</v>
+        <v>8.56</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>23.37</v>
+        <v>46.74</v>
       </c>
       <c r="T2" s="3" t="n">
         <v>159.94</v>
@@ -730,19 +730,19 @@
         <v>0</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>69.83</v>
+        <v>280.07</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>241.86</v>
+        <v>320.64</v>
       </c>
       <c r="X2" s="3" t="n">
-        <v>6.85</v>
+        <v>11.99</v>
       </c>
       <c r="Y2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>0</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AA2" s="3" t="n">
         <v>0</v>
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>8.08</v>
@@ -794,7 +794,7 @@
         <v>35.39</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>32.33</v>
+        <v>32.35</v>
       </c>
       <c r="L3" s="5" t="n">
         <v>0</v>
@@ -836,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="Y3" s="5" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="5" t="n">
         <v>44.45</v>
@@ -888,16 +888,16 @@
         <v>56.57</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>518.86</v>
+        <v>619.48</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>295.87</v>
+        <v>187.3</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1435.04</v>
+        <v>1512.07</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>1369.36</v>
@@ -906,31 +906,31 @@
         <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>741.87</v>
+        <v>511.16</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>784.39</v>
+        <v>641.45</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>47.61</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>352.44</v>
+        <v>243.87</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>13.99</v>
+        <v>69.23</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>332.2</v>
+        <v>428.32</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>13.7</v>
+        <v>23.97</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>0</v>
@@ -985,13 +985,13 @@
         <v>108.43</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>318.16</v>
+        <v>379.24</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>148.52</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>156.59</v>
+        <v>157.63</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>745.4</v>
@@ -1003,34 +1003,34 @@
         <v>0</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>549.62</v>
+        <v>529.77</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>561.59</v>
+        <v>550.1900000000001</v>
       </c>
       <c r="R5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>8</v>
+        <v>13.33</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>265.02</v>
+        <v>266.06</v>
       </c>
       <c r="U5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="V5" s="5" t="n">
-        <v>0.64</v>
+        <v>2.58</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>548.34</v>
+        <v>372.08</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>13.7</v>
+        <v>23.97</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>40789.13</v>
+        <v>23018.62</v>
       </c>
       <c r="Z5" s="5" t="n">
         <v>204.22</v>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>91.61</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>2.02</v>
+        <v>1.17</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>11.11</v>
@@ -1079,52 +1079,52 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>67.83</v>
+        <v>67.03</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>174.67</v>
+        <v>191.25</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>42.99</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>165.37</v>
+        <v>164.7</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>197.83</v>
+        <v>189.11</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>565.33</v>
+        <v>189.11</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>487.08</v>
+        <v>481.4</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>508.29</v>
+        <v>524.47</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>14.27</v>
+        <v>28.54</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>233.2</v>
+        <v>231.73</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>0.73</v>
+        <v>3.47</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>75.75</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>13.7</v>
+        <v>23.97</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>0</v>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>35.68</v>
+        <v>25.39</v>
       </c>
       <c r="M7" s="5" t="n">
         <v>0</v>
@@ -1203,10 +1203,10 @@
         <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>19.87</v>
+        <v>15.8</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>15.89</v>
+        <v>28.54</v>
       </c>
       <c r="T7" s="5" t="n">
         <v>48.52</v>
@@ -1215,16 +1215,16 @@
         <v>0</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>1.73</v>
+        <v>3.47</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>48.1</v>
+        <v>51.47</v>
       </c>
       <c r="X7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>2934.72</v>
+        <v>1520.56</v>
       </c>
       <c r="Z7" s="5" t="n">
         <v>0</v>
@@ -1273,16 +1273,16 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>136.69</v>
+        <v>65.34</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>288.62</v>
+        <v>277.95</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>80.28</v>
+        <v>149.65</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>136.33</v>
@@ -1294,34 +1294,34 @@
         <v>0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>461.32</v>
+        <v>448.69</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>491.16</v>
+        <v>512.89</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>102.32</v>
+        <v>175.8</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>50.29</v>
+        <v>106.83</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>216.97</v>
+        <v>214.99</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>2.05</v>
+        <v>10.76</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>432.76</v>
+        <v>274.68</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>13.7</v>
+        <v>23.97</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>36308.58</v>
+        <v>18682.24</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>0</v>
